--- a/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>174867.91</v>
+        <v>173060.31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1111089-481-CM25</t>
+          <t>45-389-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14340.97</v>
+        <v>11849.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>45-424-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>743345.55</v>
+        <v>10765.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1177296-517-CM25</t>
+          <t>45-437-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INGENIERÍA TICMEGA SPA</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.516.342-0</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>20496.15</v>
+        <v>24002.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>730566-562-CM25</t>
+          <t>1111089-481-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>19934.43</v>
+        <v>14590.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>730566-563-CM25</t>
+          <t>2580-1226-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>34490.66</v>
+        <v>748610.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1111089-522-CM25</t>
+          <t>45-443-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>340882.62</v>
+        <v>26582.36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5403-70-CM25</t>
+          <t>1177296-517-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CODER HUB SPA</t>
+          <t>INGENIERÍA TICMEGA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.734.221-7</t>
+          <t>76.516.342-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>53509.24</v>
+        <v>20647.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>730566-562-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>FERNANDO MARCELO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.811.563-K</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>531687.75</v>
+        <v>20081.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>730566-569-CM25</t>
+          <t>730566-563-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>FERNANDO MARCELO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
+          <t>76.811.563-K</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>67799.44</v>
+        <v>34744.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2580-1282-CM25</t>
+          <t>1111089-522-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>180843.68</v>
+        <v>339530.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>586-637-CM25</t>
+          <t>586-630-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>201043.29</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>586-675-CM25</t>
+          <t>730566-569-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,27 +1271,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>18123.34</v>
+        <v>67704.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1177296-568-CM25</t>
+          <t>2580-1282-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Toledo y Badilla Profesionales Ltda.</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.084.696-1</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12816.69</v>
+        <v>178903.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2580-1265-CM25</t>
+          <t>586-637-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,27 +1393,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.561.404-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>170450.36</v>
+        <v>198579.07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2580-1334-CM25</t>
+          <t>586-675-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,27 +1454,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>508081.52</v>
+        <v>17901.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1177296-473-CM25</t>
+          <t>1177296-568-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Toledo y Badilla Profesionales Ltda.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.084.696-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>625125.4</v>
+        <v>12800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>586-623-CM25</t>
+          <t>2580-1265-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,27 +1576,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>290759.22</v>
+        <v>171068.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1111089-726-CM25</t>
+          <t>2580-1334-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KUANTUM SPA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.553.335-K</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>31714.77</v>
+        <v>507409.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1111089-743-CM25</t>
+          <t>1177296-473-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.590.008-5</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>63785.5</v>
+        <v>626037.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>730566-612-CM25</t>
+          <t>586-623-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>28997.35</v>
+        <v>294072.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>812261-7589-CM25</t>
+          <t>1111089-726-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>KUANTUM SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.553.335-K</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>77949.86</v>
+        <v>32131.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>1111089-743-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,32 +1896,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.590.008-5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>895721.87</v>
+        <v>64624.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1111089-755-CM25</t>
+          <t>730566-612-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CORPORACION INSTITUTO MILENIO DE INVESTIGACION SOBRE LOS FUNDAMENTOS D</t>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>65.175.978-1</t>
+          <t>77.754.348-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>57567.36</v>
+        <v>29378.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>812261-7571-CM25</t>
+          <t>812261-7589-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2022,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>295182.2</v>
+        <v>78481.00999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>591-7730-SE25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,28 +2079,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>49488.86</v>
+        <v>901825.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1351461-3-CM26</t>
+          <t>1111089-755-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,22 +2119,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SERVICIOS DE SOFTWARE Y CONSULTORÍA LUIS DEL CAMPO VEJAR E.I.R.L.</t>
+          <t>CORPORACION INSTITUTO MILENIO DE INVESTIGACION SOBRE LOS FUNDAMENTOS D</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.174.186-K</t>
+          <t>65.175.978-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>52482.23</v>
+        <v>56458.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5403-3-CM26</t>
+          <t>812261-7571-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,22 +2180,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>580026</v>
+        <v>291592.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1186229-10-CM26</t>
+          <t>812261-7572-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>654773.7</v>
+        <v>48887.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1351461-5-CM26</t>
+          <t>1351461-3-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>SERVICIOS DE SOFTWARE Y CONSULTORÍA LUIS DEL CAMPO VEJAR E.I.R.L.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>77.174.186-K</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>51350.45</v>
+        <v>52201.04</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>730566-20-SE26</t>
+          <t>1186229-10-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,32 +2388,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>558501.78</v>
+        <v>664434.1899999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>812261-183-CM26</t>
+          <t>1351461-5-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2423,12 +2419,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2438,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2453,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2468,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>78226.38</v>
+        <v>52571.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>619-53-CM26</t>
+          <t>730566-20-SE26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2489,7 +2485,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2499,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2514,28 +2510,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>FERNANDO MARCELO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>72413.42999999999</v>
+        <v>556180.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1351461-11-CM26</t>
+          <t>812261-183-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>218707.38</v>
+        <v>77589.44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>812261-9882-CM25</t>
+          <t>45-527-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2606,27 +2606,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.866.212-4</t>
+          <t>96.771.610-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1722655.54</v>
+        <v>254565.52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>730566-60-CM26</t>
+          <t>45-12-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>42973.85</v>
+        <v>74806.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5403-19-CM26</t>
+          <t>45-43-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2728,27 +2728,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MT2 SPA</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.967.524-8</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2773,13 +2773,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10747.29</v>
+        <v>71839.97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1111089-40-CM26</t>
+          <t>619-53-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2789,27 +2789,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.681.168-8</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>246401.07</v>
+        <v>72334.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>1351461-11-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2850,27 +2850,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>676558.0699999999</v>
+        <v>215927.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5403-17-CM26</t>
+          <t>45-46-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2911,27 +2911,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t xml:space="preserve">ENVISION INVERSIONES LIMITADA </t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2956,13 +2956,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>203660.91</v>
+        <v>35279.98</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>730566-40-CM26</t>
+          <t>812261-9882-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2972,27 +2972,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
+          <t>77.866.212-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>497645.55</v>
+        <v>1703050.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1177296-173-CM26</t>
+          <t>730566-60-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3033,27 +3033,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>FERNANDO MARCELO</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.811.563-K</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>61554.72</v>
+        <v>42018.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1111089-140-CM26</t>
+          <t>1111089-40-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>77.681.168-8</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>65236.42</v>
+        <v>245768.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>591-155-SE26</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3185,32 +3185,28 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1641207.55</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1177296-550-CM25</t>
+          <t>730566-40-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3225,7 +3221,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3235,12 +3231,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3250,12 +3246,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3265,13 +3261,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>313385.18</v>
+        <v>498484.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1177296-198-CM26</t>
+          <t>1177296-173-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3281,17 +3277,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3311,12 +3307,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3326,13 +3322,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>21821.7</v>
+        <v>61316.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>894244-5-CM26</t>
+          <t>1111089-140-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3342,12 +3338,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3357,12 +3353,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3372,12 +3368,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NTT DATA CHILE S.A</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.886.110-7</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3387,13 +3383,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>431231.97</v>
+        <v>65024.86</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>894244-4-CM26</t>
+          <t>591-155-SE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3403,12 +3399,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3418,12 +3414,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3433,28 +3429,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1690339.34</v>
+        <v>1643132.54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5403-38-CM26</t>
+          <t>1177296-550-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3464,27 +3464,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>17021.55</v>
+        <v>316206.29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>812261-62-CM26</t>
+          <t>894244-5-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>NTT DATA CHILE S.A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>96.886.110-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,13 +3570,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>481036.15</v>
+        <v>435941.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>730566-155-CM26</t>
+          <t>1177296-198-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3631,13 +3631,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>54890.11</v>
+        <v>22060</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1111089-207-CM26</t>
+          <t>45-113-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3692,13 +3692,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>42042.6</v>
+        <v>53835.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>591-90-CM26</t>
+          <t>45-109-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>DATCO CHILE S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>96.897.630-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>914845.87</v>
+        <v>42282.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1111089-191-CM26</t>
+          <t>45-57-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3769,27 +3769,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32529.1</v>
+        <v>131137.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1177296-248-CM26</t>
+          <t>894244-4-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Toledo y Badilla Profesionales Ltda.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.084.696-1</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3875,13 +3875,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>15788.59</v>
+        <v>1696277.88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1111089-188-CM26</t>
+          <t>812261-62-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3936,7 +3936,678 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>98707.45</v>
+        <v>482098.69</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>730566-155-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.980.240-3</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.754.348-2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>55011.36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1111089-207-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.915.000-9</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.213.064-5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>41954.37</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>591-90-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>913082.5600000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1111089-191-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.915.000-9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>32466.41</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1177296-248-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Toledo y Badilla Profesionales Ltda.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.084.696-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>15535.01</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1111089-188-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>60.915.000-9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>77.173.545-2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>97132.32000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>591-86-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>1718926.68</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>45-175-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Andes Digital</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>365433.57</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1177296-280-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ZAMBONI INGENIEROS ASOCIADOS SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>78.974.330-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>8631.93</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>586-331-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CLOUDHESIVE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>77.014.934-7</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>209143.07</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>591-293-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>73717.23</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>730566-409-CM25</t>
+          <t>761-899-CM24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,27 +539,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>MAGENTA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
+          <t>76.018.273-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>173060.31</v>
+        <v>50626.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>45-389-CM25</t>
+          <t>761-898-CM24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,27 +600,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.528.848-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11849.91</v>
+        <v>163813.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>45-424-CM25</t>
+          <t>587-928-CM24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,27 +661,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>Tecnología y Servicios Informáticos Advise S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
+          <t>76.186.623-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10765.68</v>
+        <v>29869.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>45-437-CM25</t>
+          <t>2268-363-CM24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>24002.49</v>
+        <v>611852.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1111089-481-CM25</t>
+          <t>1607-237-CM24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,42 +768,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>Tecnología y Servicios Informáticos Advise S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.186.623-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>14590.77</v>
+        <v>12463.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>587-19-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>748610.75</v>
+        <v>31540.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>45-443-CM25</t>
+          <t>587-20-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,27 +905,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26582.36</v>
+        <v>39381.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1177296-517-CM25</t>
+          <t>1186229-14-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,42 +951,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INGENIERÍA TICMEGA SPA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.516.342-0</t>
+          <t>76.093.443-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>20647.1</v>
+        <v>1114399.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>730566-562-CM25</t>
+          <t>1186229-4-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>Emergya Ingenieria SL Agencia en Chile</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>59.166.580-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20081.25</v>
+        <v>1413780.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>730566-563-CM25</t>
+          <t>45-23-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,27 +1088,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>34744.68</v>
+        <v>58220.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1111089-522-CM25</t>
+          <t>619-51-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,42 +1134,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>339530.09</v>
+        <v>31915.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>586-41-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1220,17 +1220,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>10496.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>730566-569-CM25</t>
+          <t>1216094-10-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,27 +1271,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>67704.81</v>
+        <v>41405.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2580-1282-CM25</t>
+          <t>45-49-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.811.563-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>178903.18</v>
+        <v>6899.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>586-637-CM25</t>
+          <t>2268-28-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,42 +1378,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>TBUSINESS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
+          <t>77.009.886-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>198579.07</v>
+        <v>62043.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>586-675-CM25</t>
+          <t>2268-33-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,42 +1439,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>MAGNET S.P.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>76.224.628-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>17901.2</v>
+        <v>248945.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1177296-568-CM25</t>
+          <t>2268-45-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,42 +1500,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Toledo y Badilla Profesionales Ltda.</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.084.696-1</t>
+          <t>77.842.230-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12800</v>
+        <v>327494.66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2580-1265-CM25</t>
+          <t>2268-53-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,42 +1561,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>171068.81</v>
+        <v>18870.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2580-1334-CM25</t>
+          <t>2268-40-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,42 +1622,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>IT4U</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.877.740-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>507409.75</v>
+        <v>26887.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1177296-473-CM25</t>
+          <t>45-50-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,27 +1698,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>626037.92</v>
+        <v>35305.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>586-623-CM25</t>
+          <t>45-85-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.046.871-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>294072.23</v>
+        <v>18919.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1111089-726-CM25</t>
+          <t>2268-70-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,27 +1820,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>KUANTUM SPA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.553.335-K</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>32131.97</v>
+        <v>42994.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1111089-743-CM25</t>
+          <t>812261-1322-CM24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,42 +1866,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.590.008-5</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>64624.59</v>
+        <v>262605.26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>730566-612-CM25</t>
+          <t>812261-1268-CM24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>29378.8</v>
+        <v>138546.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>812261-7589-CM25</t>
+          <t>587-168-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>78481.00999999999</v>
+        <v>18729.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>1607-86-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,32 +2049,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2087,24 +2087,20 @@
           <t>77.430.680-3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>901825.33</v>
+        <v>629930.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1111089-755-CM25</t>
+          <t>45-110-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,42 +2110,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CORPORACION INSTITUTO MILENIO DE INVESTIGACION SOBRE LOS FUNDAMENTOS D</t>
+          <t>ACS INGENIEROS SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>65.175.978-1</t>
+          <t>76.240.927-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>56458.54</v>
+        <v>24277.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>812261-7571-CM25</t>
+          <t>761-234-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,27 +2186,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>291592.37</v>
+        <v>24718.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>45-103-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,27 +2247,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>48887.01</v>
+        <v>122490.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1351461-3-CM26</t>
+          <t>2268-106-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,42 +2293,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SERVICIOS DE SOFTWARE Y CONSULTORÍA LUIS DEL CAMPO VEJAR E.I.R.L.</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.174.186-K</t>
+          <t>77.842.230-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>52201.04</v>
+        <v>236229.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1186229-10-CM26</t>
+          <t>1607-93-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>664434.1899999999</v>
+        <v>705074.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1351461-5-CM26</t>
+          <t>587-197-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,27 +2430,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>52571.41</v>
+        <v>21169.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>730566-20-SE26</t>
+          <t>587-167-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,47 +2491,43 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>556180.29</v>
+        <v>834321.6800000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>812261-183-CM26</t>
+          <t>45-159-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2545,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2560,27 +2552,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>96.771.610-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2590,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>77589.44</v>
+        <v>26225.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>45-527-CM25</t>
+          <t>812261-4748-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2606,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2621,27 +2613,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2651,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>254565.52</v>
+        <v>40027.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>45-12-CM26</t>
+          <t>761-340-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2667,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2682,27 +2674,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2712,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>74806.8</v>
+        <v>123735.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>45-43-CM26</t>
+          <t>2268-132-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2728,42 +2720,42 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2773,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>71839.97</v>
+        <v>819024.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>619-53-CM26</t>
+          <t>587-375-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2789,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2804,27 +2796,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>KUANTUM SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.553.335-K</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2834,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>72334.02</v>
+        <v>32030.67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1351461-11-CM26</t>
+          <t>761-328-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2850,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2865,27 +2857,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.093.443-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2895,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>215927.46</v>
+        <v>1601122.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>45-46-CM26</t>
+          <t>587-376-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2911,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2926,27 +2918,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENVISION INVERSIONES LIMITADA </t>
+          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
+          <t>76.004.023-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2956,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>35279.98</v>
+        <v>39773.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>812261-9882-CM25</t>
+          <t>45-204-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2972,42 +2964,42 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
+          <t>SERVICIOS DE CONSULTORIA VALPOSYSTEMS LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.866.212-4</t>
+          <t>76.164.712-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3017,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1703050.45</v>
+        <v>27383.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>730566-60-CM26</t>
+          <t>591-7471-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3033,42 +3025,42 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3078,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>42018.78</v>
+        <v>1564746.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1111089-40-CM26</t>
+          <t>586-411-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3094,42 +3086,42 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
+          <t>ALFAPEOPLE CHILE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.681.168-8</t>
+          <t>76.360.577-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3139,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>245768.22</v>
+        <v>16969.91</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>586-289-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3155,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3170,27 +3162,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3200,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>681911.34</v>
+        <v>668180.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>730566-40-CM26</t>
+          <t>587-337-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3216,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3231,27 +3223,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3261,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>498484.99</v>
+        <v>125178.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1177296-173-CM26</t>
+          <t>45-217-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3277,32 +3269,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3322,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>61316.16</v>
+        <v>156370.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1111089-140-CM26</t>
+          <t>587-393-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3338,42 +3330,42 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.734.221-7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3383,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>65024.86</v>
+        <v>570339.21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>591-155-SE26</t>
+          <t>586-371-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3399,62 +3391,58 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.011.398-0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1643132.54</v>
+        <v>232720.03</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1177296-550-CM25</t>
+          <t>586-456-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3464,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3479,27 +3467,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3509,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>316206.29</v>
+        <v>143486.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>894244-5-CM26</t>
+          <t>586-382-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3525,42 +3513,42 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NTT DATA CHILE S.A</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.886.110-7</t>
+          <t>77.347.464-8</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>435941.1</v>
+        <v>143852.31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1177296-198-CM26</t>
+          <t>761-577-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3586,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3601,27 +3589,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3631,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>22060</v>
+        <v>11084.79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>45-113-CM26</t>
+          <t>586-404-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3647,42 +3635,42 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3692,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>53835.73</v>
+        <v>45751.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>45-109-CM26</t>
+          <t>587-489-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3708,42 +3696,42 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DATCO CHILE S A</t>
+          <t>ALFAPEOPLE CHILE SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.897.630-3</t>
+          <t>76.360.577-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3753,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>42282.45</v>
+        <v>315184.35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>45-57-CM26</t>
+          <t>45-325-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3769,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3794,17 +3782,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.811.563-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3814,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>131137.6</v>
+        <v>41786.86</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>894244-4-CM26</t>
+          <t>761-611-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3830,42 +3818,42 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3875,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1696277.88</v>
+        <v>19499.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>812261-62-CM26</t>
+          <t>586-402-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3891,42 +3879,42 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3936,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>482098.69</v>
+        <v>193181.61</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>730566-155-CM26</t>
+          <t>586-370-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3952,42 +3940,42 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3997,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>55011.36</v>
+        <v>151581.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1111089-207-CM26</t>
+          <t>2268-226-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4013,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4028,27 +4016,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
+          <t>77.842.230-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4058,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>41954.37</v>
+        <v>987188.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>591-90-CM26</t>
+          <t>45-349-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4074,42 +4062,42 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4119,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>913082.5600000001</v>
+        <v>41671.09</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1111089-191-CM26</t>
+          <t>761-628-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4135,42 +4123,42 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4180,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>32466.41</v>
+        <v>40057.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1177296-248-CM26</t>
+          <t>45-353-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4196,42 +4184,42 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Toledo y Badilla Profesionales Ltda.</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.084.696-1</t>
+          <t>76.734.221-7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4241,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>15535.01</v>
+        <v>46383.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1111089-188-CM26</t>
+          <t>45-371-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4257,42 +4245,42 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>OG CONSULTORES</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
+          <t>76.367.662-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4302,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>97132.32000000001</v>
+        <v>57148.85</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>587-603-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4318,42 +4306,42 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4363,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1718926.68</v>
+        <v>9842.209999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>45-175-CM26</t>
+          <t>45-372-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4379,17 +4367,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4409,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>INVERSIONES ENVISION CL SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>77.733.311-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4424,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>365433.57</v>
+        <v>29714.89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1177296-280-CM26</t>
+          <t>45-374-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4440,27 +4428,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4470,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ZAMBONI INGENIEROS ASOCIADOS SPA</t>
+          <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.974.330-4</t>
+          <t>76.098.050-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4485,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>8631.93</v>
+        <v>58752.07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>586-331-CM26</t>
+          <t>45-389-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4501,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4516,27 +4504,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4546,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>209143.07</v>
+        <v>11849.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>591-293-CM26</t>
+          <t>45-424-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4562,42 +4550,42 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4607,6 +4595,2576 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
+        <v>10765.68</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>45-437-CM25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ANDES DIGITAL</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>24002.49</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>587-654-CM25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.801.000-7</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>32268.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>45-443-CM25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ANDES DIGITAL</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>26582.36</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>586-630-CM25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>530945.6899999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>587-660-CM25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.801.000-7</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>33144.53</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>586-637-CM25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.561.404-k</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>198579.07</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>586-675-CM25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.011.651-3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>17901.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>586-623-CM25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>CLOUDHESIVE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>77.014.934-7</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>294072.23</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>812261-7589-CM25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>78481.00999999999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>591-7730-SE25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Tecnova</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>901825.33</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>812261-7571-CM25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>291592.37</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>812261-7572-CM25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>48887.01</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1351461-3-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>SERVICIOS DE SOFTWARE Y CONSULTORÍA LUIS DEL CAMPO VEJAR E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>77.174.186-K</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>52201.04</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1186229-10-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.002.000-3</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Pragma Informatica S.A.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>664434.1899999999</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1351461-5-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Asimov Consultores SpA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>76.372.725-4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>52571.41</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>761-31-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>60.515.000-4</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>ANDES DIGITAL</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>26845.29</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>812261-183-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>77589.44</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>45-527-CM25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>ANTICIPA S A</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>254565.52</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>761-827-CM25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>60.515.000-4</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.185.219-1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>46399.86</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>45-12-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ANDES DIGITAL</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>74806.8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>45-43-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>RIALIS SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.348.639-7</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>71839.97</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>619-53-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>COMPUNET S.P.A.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>78.466.220-9</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>72334.02</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>587-61-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.801.000-7</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Asimov Consultores SpA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.372.725-4</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>80753.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1351461-11-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Asimov Consultores SpA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.372.725-4</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>215927.46</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>45-46-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENVISION INVERSIONES LIMITADA </t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.693.295-9</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>35279.98</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>812261-9882-CM25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>77.866.212-4</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>1703050.45</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1186229-57-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.002.000-3</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Pragma Informatica S.A.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>681911.34</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>591-155-SE26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>ANTICIPA S A</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>1643132.54</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2268-87-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61.608.700-2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>TBUSINESS SPA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>77.009.886-6</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>63895.88</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>894244-5-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>NTT DATA CHILE S.A</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>96.886.110-7</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>435941.1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>45-113-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>53835.73</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>45-109-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>DATCO CHILE S A</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>96.897.630-3</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>42282.45</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2268-97-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>61.608.700-2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>83990.07000000001</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>45-57-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>131137.6</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>894244-4-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>1696277.88</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>812261-62-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>482098.69</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>591-90-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>913082.5600000001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>591-86-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>1718926.68</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>45-175-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Andes Digital</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>365433.57</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1607-76-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>BINARY BAG</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.848.560-7</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>752030.39</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>586-331-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>CLOUDHESIVE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>77.014.934-7</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>209143.07</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>591-293-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
         <v>73717.23</v>
       </c>
     </row>

--- a/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desarrollo-y-man top org" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="desarrollo-y-man top org" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>45-23-CM25</t>
+          <t>619-51-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,27 +1088,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>58220.51</v>
+        <v>31915.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>619-51-CM25</t>
+          <t>586-41-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,27 +1149,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31915.79</v>
+        <v>10496.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>586-41-CM25</t>
+          <t>1216094-10-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,27 +1210,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10496.08</v>
+        <v>41405.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1216094-10-CM25</t>
+          <t>2268-28-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>TBUSINESS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>77.009.886-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>41405.99</v>
+        <v>62043.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>45-49-CM25</t>
+          <t>2268-33-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,42 +1317,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Fernando Marcelo</t>
+          <t>MAGNET S.P.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>76.224.628-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6899.86</v>
+        <v>248945.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2268-28-CM25</t>
+          <t>2268-45-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TBUSINESS SPA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.009.886-6</t>
+          <t>77.842.230-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>62043.21</v>
+        <v>327494.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2268-33-CM25</t>
+          <t>2268-53-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MAGNET S.P.A.</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.224.628-7</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>248945.81</v>
+        <v>18870.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2268-45-CM25</t>
+          <t>2268-40-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>IT4U</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
+          <t>76.877.740-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>327494.66</v>
+        <v>26887.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2268-53-CM25</t>
+          <t>2268-70-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.489.853-2</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>18870.52</v>
+        <v>42994.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2268-40-CM25</t>
+          <t>812261-1322-CM24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,42 +1622,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IT4U</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.877.740-3</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>26887.43</v>
+        <v>262605.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45-50-CM25</t>
+          <t>812261-1268-CM24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,27 +1698,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>35305.18</v>
+        <v>138546.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45-85-CM25</t>
+          <t>587-168-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Diseño y Desarrollo Visualmente SpA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>18919.17</v>
+        <v>18729.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2268-70-CM25</t>
+          <t>1607-86-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,37 +1810,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>42994.6</v>
+        <v>629930.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>812261-1322-CM24</t>
+          <t>761-234-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>262605.26</v>
+        <v>24718.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>812261-1268-CM24</t>
+          <t>2268-106-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,42 +1927,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.842.230-1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>138546.34</v>
+        <v>236229.85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>587-168-CM25</t>
+          <t>1607-93-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18729.48</v>
+        <v>705074.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1607-86-CM25</t>
+          <t>587-197-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,27 +2064,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>629930.14</v>
+        <v>21169.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>45-110-CM25</t>
+          <t>587-167-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ACS INGENIEROS SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.240.927-5</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>24277.12</v>
+        <v>834321.6800000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>761-234-CM25</t>
+          <t>812261-4748-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>24718.17</v>
+        <v>40027.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>45-103-CM25</t>
+          <t>761-340-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,27 +2247,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>122490.05</v>
+        <v>123735.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2268-106-CM25</t>
+          <t>2268-132-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2318,17 +2318,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>236229.85</v>
+        <v>819024.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1607-93-CM25</t>
+          <t>587-375-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>KUANTUM SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.553.335-K</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>705074.45</v>
+        <v>32030.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>587-197-CM25</t>
+          <t>761-328-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ENVISION INVERSIONES LIMITADA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
+          <t>76.093.443-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>21169.75</v>
+        <v>1601122.18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>587-167-CM25</t>
+          <t>587-376-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.004.023-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>834321.6800000001</v>
+        <v>39773.91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45-159-CM25</t>
+          <t>591-7471-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,42 +2537,42 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26225.06</v>
+        <v>1564746.61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>812261-4748-CM25</t>
+          <t>586-411-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>ALFAPEOPLE CHILE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.360.577-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>40027.16</v>
+        <v>16969.91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>761-340-CM25</t>
+          <t>586-289-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,42 +2659,42 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>123735.3</v>
+        <v>668180.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2268-132-CM25</t>
+          <t>587-337-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,42 +2720,42 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>819024.72</v>
+        <v>125178.61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>587-375-CM25</t>
+          <t>587-393-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>KUANTUM SPA</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.553.335-K</t>
+          <t>76.734.221-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>32030.67</v>
+        <v>570339.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>761-328-CM25</t>
+          <t>586-371-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,27 +2857,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1601122.18</v>
+        <v>232720.03</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>587-376-CM25</t>
+          <t>586-456-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,27 +2918,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.004.023-1</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>39773.91</v>
+        <v>143486.24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>45-204-CM25</t>
+          <t>586-382-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,27 +2979,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CONSULTORIA VALPOSYSTEMS LIMITADA</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.164.712-1</t>
+          <t>77.347.464-8</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>27383.24</v>
+        <v>143852.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>591-7471-CM25</t>
+          <t>761-577-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,42 +3025,42 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1564746.61</v>
+        <v>11084.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>586-411-CM25</t>
+          <t>586-404-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ALFAPEOPLE CHILE SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.360.577-9</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16969.91</v>
+        <v>45751.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>586-289-CM25</t>
+          <t>587-489-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,42 +3147,42 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>ALFAPEOPLE CHILE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.360.577-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>668180.4</v>
+        <v>315184.35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>587-337-CM25</t>
+          <t>2580-1108-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,27 +3223,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>125178.61</v>
+        <v>365454.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>45-217-CM25</t>
+          <t>761-611-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>156370.06</v>
+        <v>19499.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>587-393-CM25</t>
+          <t>586-370-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,27 +3345,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CODER HUB SPA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.734.221-7</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>570339.21</v>
+        <v>151581.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>586-371-CM25</t>
+          <t>586-402-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>232720.03</v>
+        <v>193181.61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>586-456-CM25</t>
+          <t>2268-226-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,42 +3452,42 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>77.842.230-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>143486.24</v>
+        <v>987188.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>586-382-CM25</t>
+          <t>761-628-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,27 +3528,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>USERCODE SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.347.464-8</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>143852.31</v>
+        <v>40057.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>761-577-CM25</t>
+          <t>587-603-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,27 +3589,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11084.79</v>
+        <v>9842.209999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>586-404-CM25</t>
+          <t>2580-1226-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,27 +3650,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>45751.4</v>
+        <v>748610.75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>587-489-CM25</t>
+          <t>587-654-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3721,17 +3721,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ALFAPEOPLE CHILE SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.360.577-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>315184.35</v>
+        <v>32268.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>45-325-CM25</t>
+          <t>586-630-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,27 +3772,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Fernando Marcelo</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41786.86</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>761-611-CM25</t>
+          <t>587-660-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,42 +3818,42 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>19499.99</v>
+        <v>33144.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>586-402-CM25</t>
+          <t>2580-1282-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>193181.61</v>
+        <v>178903.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>586-370-CM25</t>
+          <t>586-637-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.561.404-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>151581.75</v>
+        <v>198579.07</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2268-226-CM25</t>
+          <t>586-675-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,42 +4001,42 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>987188.39</v>
+        <v>17901.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>45-349-CM25</t>
+          <t>2580-1265-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,27 +4077,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>41671.09</v>
+        <v>171068.81</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>761-628-CM25</t>
+          <t>2580-1334-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>40057.03</v>
+        <v>507409.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>45-353-CM25</t>
+          <t>586-623-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CODER HUB SPA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.734.221-7</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>46383.83</v>
+        <v>294072.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>45-371-CM25</t>
+          <t>812261-7589-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,27 +4260,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>OG CONSULTORES</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.367.662-5</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>57148.85</v>
+        <v>78481.00999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>587-603-CM25</t>
+          <t>591-7730-SE25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,58 +4306,62 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9842.209999999999</v>
+        <v>901825.33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>45-372-CM25</t>
+          <t>812261-7571-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4371,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,27 +4386,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>INVERSIONES ENVISION CL SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.733.311-9</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>29714.89</v>
+        <v>291592.37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>45-374-CM25</t>
+          <t>812261-7572-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4432,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,27 +4447,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.098.050-1</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>58752.07</v>
+        <v>48887.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>45-389-CM25</t>
+          <t>1351461-3-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4493,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4508,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4523,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SERVICIOS DE SOFTWARE Y CONSULTORÍA LUIS DEL CAMPO VEJAR E.I.R.L.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.174.186-K</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>11849.91</v>
+        <v>52201.04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>45-424-CM25</t>
+          <t>1186229-10-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4554,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4569,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>10765.68</v>
+        <v>664434.1899999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>45-437-CM25</t>
+          <t>1351461-5-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4615,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4630,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4645,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>24002.49</v>
+        <v>52571.41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>587-654-CM25</t>
+          <t>761-31-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4676,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4691,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4706,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>32268.6</v>
+        <v>26845.29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>45-443-CM25</t>
+          <t>812261-183-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4737,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4752,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4767,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26582.36</v>
+        <v>77589.44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>761-827-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4798,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,27 +4813,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>46399.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>587-660-CM25</t>
+          <t>619-53-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,27 +4859,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4889,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>33144.53</v>
+        <v>72334.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>586-637-CM25</t>
+          <t>587-61-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4920,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,27 +4935,27 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>198579.07</v>
+        <v>80753.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>586-675-CM25</t>
+          <t>1351461-11-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4981,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,27 +4996,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>17901.2</v>
+        <v>215927.46</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>586-623-CM25</t>
+          <t>812261-9882-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,42 +5042,42 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>77.866.212-4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>294072.23</v>
+        <v>1703050.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>812261-7589-CM25</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,27 +5103,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5133,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>78481.00999999999</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>591-155-SE26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5164,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5190,17 +5194,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>96.771.610-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5209,13 +5213,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>901825.33</v>
+        <v>1643132.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>812261-7571-CM25</t>
+          <t>2268-87-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5225,27 +5229,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5255,12 +5259,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>TBUSINESS SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.009.886-6</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5270,13 +5274,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>291592.37</v>
+        <v>63895.88</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>894244-5-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5286,27 +5290,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5316,12 +5320,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>NTT DATA CHILE S.A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>96.886.110-7</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5331,13 +5335,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>48887.01</v>
+        <v>435941.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1351461-3-CM26</t>
+          <t>2268-97-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5347,27 +5351,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5377,12 +5381,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SERVICIOS DE SOFTWARE Y CONSULTORÍA LUIS DEL CAMPO VEJAR E.I.R.L.</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.174.186-K</t>
+          <t>77.842.230-1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5392,13 +5396,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>52201.04</v>
+        <v>83990.07000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1186229-10-CM26</t>
+          <t>894244-4-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5408,27 +5412,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5438,12 +5442,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5453,13 +5457,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>664434.1899999999</v>
+        <v>1696277.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1351461-5-CM26</t>
+          <t>812261-62-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5469,27 +5473,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5503,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5518,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>52571.41</v>
+        <v>482098.69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>761-31-CM26</t>
+          <t>591-90-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5530,27 +5534,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5564,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5579,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>26845.29</v>
+        <v>913082.5600000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>812261-183-CM26</t>
+          <t>591-86-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5591,42 +5595,42 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,13 +5640,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>77589.44</v>
+        <v>1718926.68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>45-527-CM25</t>
+          <t>1607-76-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5652,42 +5656,42 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>BINARY BAG</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
+          <t>76.848.560-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5697,13 +5701,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>254565.52</v>
+        <v>752030.39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>761-827-CM25</t>
+          <t>586-331-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5713,12 +5717,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5728,27 +5732,27 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5758,13 +5762,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>46399.86</v>
+        <v>209143.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>45-12-CM26</t>
+          <t>591-293-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5774,42 +5778,42 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5819,1352 +5823,6 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>74806.8</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>45-43-CM26</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>61.531.000-K</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>RIALIS SPA</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>76.348.639-7</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>71839.97</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>619-53-CM26</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>60.801.000-9</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>COMPUNET S.P.A.</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>72334.02</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>587-61-CM26</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>61.801.000-7</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Asimov Consultores SpA</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>76.372.725-4</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>80753.5</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>1351461-11-CM26</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>mar-2026</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>60.801.000-9</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Asimov Consultores SpA</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>76.372.725-4</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>215927.46</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>45-46-CM26</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>mar-2026</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>61.531.000-K</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ENVISION INVERSIONES LIMITADA </t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>76.693.295-9</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>35279.98</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>812261-9882-CM25</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>mar-2026</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>65.075.485-9</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>77.866.212-4</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>1703050.45</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>1186229-57-CM26</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>61.002.000-3</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Pragma Informatica S.A.</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>681911.34</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>591-155-SE26</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>61.603.000-0</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>FONDO NACIONAL DE SALUD</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>ANTICIPA S A</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>1643132.54</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2268-87-CM26</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>61.608.700-2</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>TBUSINESS SPA</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>77.009.886-6</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>63895.88</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>894244-5-CM26</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>60.801.000-9</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>NTT DATA CHILE S.A</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>96.886.110-7</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>435941.1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>45-113-CM26</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>61.531.000-K</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>53835.73</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>45-109-CM26</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>61.531.000-K</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>DATCO CHILE S A</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>96.897.630-3</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>42282.45</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2268-97-CM26</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>61.608.700-2</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>77.842.230-1</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>83990.07000000001</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>45-57-CM26</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>61.531.000-K</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>131137.6</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>894244-4-CM26</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>60.801.000-9</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>SONDA S A</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>1696277.88</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>812261-62-CM26</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>65.075.485-9</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Kibernum S.A</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>482098.69</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>591-90-CM26</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>61.603.000-0</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>FONDO NACIONAL DE SALUD</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>SONDA S A</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>913082.5600000001</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>591-86-CM26</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>61.603.000-0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>FONDO NACIONAL DE SALUD</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>APIUX TECNOLOGIA SPA</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>76.516.485-0</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>1718926.68</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>45-175-CM26</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>61.531.000-K</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Andes Digital</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>365433.57</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>1607-76-CM26</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>61.509.000-k</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>BINARY BAG</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>76.848.560-7</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>752030.39</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>586-331-CM26</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>60.804.000-5</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>77.014.934-7</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>209143.07</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>591-293-CM26</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>61.603.000-0</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>FONDO NACIONAL DE SALUD</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="n">
         <v>73717.23</v>
       </c>
     </row>

--- a/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3625,7 +3625,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>587-654-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>748610.75</v>
+        <v>32268.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>587-654-CM25</t>
+          <t>2580-1226-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>32268.6</v>
+        <v>748610.75</v>
       </c>
     </row>
     <row r="55">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5824,6 +5824,189 @@
       </c>
       <c r="M88" s="2" t="n">
         <v>73717.23</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>586-410-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>XMS Business Solutions S.A.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>16165.58</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2268-138-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.608.700-2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>CRUD SPA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>77.142.835-5</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>73043.13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>761-270-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>60.515.000-4</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.011.651-3</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>128378.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.018.273-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.516.485-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>76.093.443-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1436,11 @@
           <t>77.842.230-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1490,7 +1514,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2268-40-CM25</t>
+          <t>730566-108-SE25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1529,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,28 +1554,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IT4U</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.877.740-3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>26887.43</v>
+        <v>34047.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2268-70-CM25</t>
+          <t>2268-40-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1589,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1591,12 +1619,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>IT4U</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.877.740-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1634,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>42994.6</v>
+        <v>26887.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>812261-1322-CM24</t>
+          <t>2268-70-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1655,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1680,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1695,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>262605.26</v>
+        <v>42994.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>812261-1268-CM24</t>
+          <t>812261-1322-CM24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,13 +1756,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>138546.34</v>
+        <v>262605.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>587-168-CM25</t>
+          <t>812261-1268-CM24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1777,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1787,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1802,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1817,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>18729.48</v>
+        <v>138546.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1607-86-CM25</t>
+          <t>587-168-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1838,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1848,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1863,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>629930.14</v>
+        <v>18729.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>761-234-CM25</t>
+          <t>1607-86-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1903,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1913,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,28 +1928,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>24718.17</v>
+        <v>629930.14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2268-106-CM25</t>
+          <t>761-234-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1963,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1993,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +2008,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>236229.85</v>
+        <v>24718.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1607-93-CM25</t>
+          <t>730566-177-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2029,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2039,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,28 +2054,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>705074.45</v>
+        <v>39665.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>587-197-CM25</t>
+          <t>2268-106-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,22 +2094,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,28 +2119,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ENVISION INVERSIONES LIMITADA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21169.75</v>
+        <v>236229.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>587-167-CM25</t>
+          <t>1607-93-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2154,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2169,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,28 +2184,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>834321.6800000001</v>
+        <v>705074.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>812261-4748-CM25</t>
+          <t>587-197-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2219,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2234,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2249,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2264,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>40027.16</v>
+        <v>21169.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>761-340-CM25</t>
+          <t>730566-248-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2280,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2295,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,28 +2310,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>123735.3</v>
+        <v>44731.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2268-132-CM25</t>
+          <t>587-167-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2345,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,28 +2375,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>819024.72</v>
+        <v>834321.6800000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>587-375-CM25</t>
+          <t>812261-4748-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2415,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2425,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,28 +2440,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>KUANTUM SPA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.553.335-K</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>32030.67</v>
+        <v>40027.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>761-328-CM25</t>
+          <t>730566-292-SE25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2480,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2490,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2505,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1601122.18</v>
+        <v>31755.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>587-376-CM25</t>
+          <t>761-340-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2540,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2555,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2570,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.004.023-1</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2585,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>39773.91</v>
+        <v>123735.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>591-7471-CM25</t>
+          <t>730566-303-SE25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,58 +2601,62 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1564746.61</v>
+        <v>32162.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>586-411-CM25</t>
+          <t>2268-132-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,58 +2666,62 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ALFAPEOPLE CHILE SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.360.577-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>16969.91</v>
+        <v>819024.72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>586-289-CM25</t>
+          <t>587-375-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,42 +2731,42 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>KUANTUM SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.553.335-K</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2776,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>668180.4</v>
+        <v>32030.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>587-337-CM25</t>
+          <t>730566-338-SE25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2792,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2807,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,28 +2822,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>125178.61</v>
+        <v>15430.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>587-393-CM25</t>
+          <t>730566-333-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2857,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2872,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2887,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CODER HUB SPA</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.734.221-7</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2902,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>570339.21</v>
+        <v>49976.79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>586-371-CM25</t>
+          <t>761-328-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2918,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,43 +2933,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>232720.03</v>
+        <v>1601122.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>586-456-CM25</t>
+          <t>587-376-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2988,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,27 +2998,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.004.023-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3028,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>143486.24</v>
+        <v>39773.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>586-382-CM25</t>
+          <t>591-7471-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,53 +3049,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>USERCODE SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.347.464-8</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>143852.31</v>
+        <v>1564746.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>761-577-CM25</t>
+          <t>586-411-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3109,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,27 +3124,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>ALFAPEOPLE CHILE SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.360.577-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3154,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11084.79</v>
+        <v>16969.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>586-404-CM25</t>
+          <t>586-289-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,17 +3170,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3116,12 +3200,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3215,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>45751.4</v>
+        <v>668180.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>587-489-CM25</t>
+          <t>587-337-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3231,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,28 +3261,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ALFAPEOPLE CHILE SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.360.577-9</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>315184.35</v>
+        <v>125178.61</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2580-1108-CM25</t>
+          <t>587-393-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3296,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3311,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,28 +3326,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.734.221-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>365454.67</v>
+        <v>570339.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>761-611-CM25</t>
+          <t>730566-376-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3361,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3376,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,28 +3391,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>19499.99</v>
+        <v>28831.79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>586-370-CM25</t>
+          <t>586-371-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3426,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3360,12 +3456,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3471,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>151581.75</v>
+        <v>232720.03</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>586-402-CM25</t>
+          <t>586-456-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3487,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3421,12 +3517,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3532,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>193181.61</v>
+        <v>143486.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2268-226-CM25</t>
+          <t>586-382-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,58 +3548,62 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>77.347.464-8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>987188.39</v>
+        <v>143852.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>761-628-CM25</t>
+          <t>761-577-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3613,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3543,12 +3643,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3658,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>40057.03</v>
+        <v>11084.79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>587-603-CM25</t>
+          <t>586-404-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3674,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,27 +3689,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3719,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>9842.209999999999</v>
+        <v>45751.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>587-654-CM25</t>
+          <t>587-489-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3735,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3665,12 +3765,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>ALFAPEOPLE CHILE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.360.577-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3780,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>32268.6</v>
+        <v>315184.35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>761-611-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3796,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3811,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3826,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3841,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>748610.75</v>
+        <v>19499.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>586-370-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3857,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3787,12 +3887,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3902,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>151581.75</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>587-660-CM25</t>
+          <t>586-402-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3918,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,27 +3933,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3963,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>33144.53</v>
+        <v>193181.61</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2580-1282-CM25</t>
+          <t>2268-226-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,27 +3979,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,28 +4009,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>178903.18</v>
+        <v>987188.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>586-637-CM25</t>
+          <t>761-628-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +4044,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,43 +4059,47 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>198579.07</v>
+        <v>40057.03</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>586-675-CM25</t>
+          <t>730566-477-SE25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4109,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,43 +4124,47 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>ADVANSOLUTION TECNOLOGIA LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>76.005.406-2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>17901.2</v>
+        <v>34642.81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2580-1265-CM25</t>
+          <t>587-603-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4174,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4189,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4204,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4219,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>171068.81</v>
+        <v>9842.209999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2580-1334-CM25</t>
+          <t>730566-409-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4235,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4250,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4265,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4280,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>507409.75</v>
+        <v>173060.31</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>586-623-CM25</t>
+          <t>587-654-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4296,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,43 +4311,47 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>294072.23</v>
+        <v>32268.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>812261-7589-CM25</t>
+          <t>730566-562-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4361,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4376,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,28 +4391,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>78481.00999999999</v>
+        <v>20081.25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>730566-563-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,27 +4426,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4456,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.811.563-K</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4355,13 +4475,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>901825.33</v>
+        <v>34744.68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>812261-7571-CM25</t>
+          <t>586-630-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4371,12 +4491,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,27 +4506,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4416,13 +4536,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>291592.37</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>730566-569-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4432,12 +4552,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4447,12 +4567,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4462,12 +4582,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4477,13 +4597,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>48887.01</v>
+        <v>67704.81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1351461-3-CM26</t>
+          <t>587-660-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4493,12 +4613,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4508,12 +4628,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4523,28 +4643,32 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SERVICIOS DE SOFTWARE Y CONSULTORÍA LUIS DEL CAMPO VEJAR E.I.R.L.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.174.186-K</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>52201.04</v>
+        <v>33144.53</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1186229-10-CM26</t>
+          <t>586-637-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4554,12 +4678,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4569,27 +4693,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.561.404-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4723,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>664434.1899999999</v>
+        <v>198579.07</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1351461-5-CM26</t>
+          <t>586-675-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4615,12 +4739,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4630,27 +4754,27 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,13 +4784,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>52571.41</v>
+        <v>17901.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>761-31-CM26</t>
+          <t>586-623-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4676,12 +4800,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4691,27 +4815,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4845,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>26845.29</v>
+        <v>294072.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>812261-183-CM26</t>
+          <t>730566-612-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4737,12 +4861,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,12 +4876,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4767,28 +4891,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>77.754.348-2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>77589.44</v>
+        <v>29378.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>761-827-CM25</t>
+          <t>591-7730-SE25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4798,27 +4926,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,28 +4956,32 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>46399.86</v>
+        <v>901825.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>619-53-CM26</t>
+          <t>812261-7589-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4859,12 +4991,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4874,12 +5006,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,28 +5021,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>72334.02</v>
+        <v>78481.00999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>587-61-CM26</t>
+          <t>761-834-SE25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4920,12 +5056,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +5071,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4950,28 +5086,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>MAGENTA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>76.018.273-7</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>80753.5</v>
+        <v>17222.22</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1351461-11-CM26</t>
+          <t>812261-7571-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4981,12 +5121,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +5136,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,12 +5151,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5026,13 +5166,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>215927.46</v>
+        <v>291592.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>812261-9882-CM25</t>
+          <t>812261-7572-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5042,17 +5182,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5072,12 +5212,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.866.212-4</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5087,13 +5227,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1703050.45</v>
+        <v>48887.01</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>1351461-3-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,27 +5243,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5133,12 +5273,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>SERVICIOS DE SOFTWARE Y CONSULTORÍA LUIS DEL CAMPO VEJAR E.I.R.L.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.174.186-K</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,13 +5288,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>681911.34</v>
+        <v>52201.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>591-155-SE26</t>
+          <t>1186229-10-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5164,27 +5304,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5194,12 +5334,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5213,13 +5353,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1643132.54</v>
+        <v>664434.1899999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2268-87-CM26</t>
+          <t>1351461-5-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5229,27 +5369,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5259,12 +5399,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>TBUSINESS SPA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.009.886-6</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5274,13 +5414,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>63895.88</v>
+        <v>52571.41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>894244-5-CM26</t>
+          <t>761-31-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5290,27 +5430,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5320,12 +5460,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>NTT DATA CHILE S.A</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.886.110-7</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5335,13 +5475,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>435941.1</v>
+        <v>26845.29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2268-97-CM26</t>
+          <t>730566-20-SE26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5351,27 +5491,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5381,28 +5521,32 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>83990.07000000001</v>
+        <v>556180.29</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>894244-4-CM26</t>
+          <t>812261-183-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5412,27 +5556,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5442,28 +5586,32 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1696277.88</v>
+        <v>77589.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>812261-62-CM26</t>
+          <t>761-827-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5473,27 +5621,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5503,12 +5651,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5518,13 +5666,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>482098.69</v>
+        <v>46399.86</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>591-90-CM26</t>
+          <t>619-53-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5534,42 +5682,42 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5579,13 +5727,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>913082.5600000001</v>
+        <v>72334.02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>587-61-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5595,42 +5743,42 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5640,13 +5788,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1718926.68</v>
+        <v>80753.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1607-76-CM26</t>
+          <t>1351461-11-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5656,42 +5804,42 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>BINARY BAG</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.848.560-7</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5701,13 +5849,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>752030.39</v>
+        <v>215927.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>586-331-CM26</t>
+          <t>812261-9882-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5717,58 +5865,62 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>TECNOLOGIA Y TELECOMUNICACIONES  SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>77.866.212-4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>209143.07</v>
+        <v>1703050.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>591-293-CM26</t>
+          <t>730566-60-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5778,58 +5930,62 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>73717.23</v>
+        <v>42018.78</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>586-410-CM26</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5839,12 +5995,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5854,43 +6010,47 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>XMS Business Solutions S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.249.938-k</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>16165.58</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2268-138-CM26</t>
+          <t>730566-40-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5900,27 +6060,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5930,12 +6090,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CRUD SPA</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.142.835-5</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5945,68 +6105,1011 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>73043.13</v>
+        <v>498484.99</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>591-155-SE26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>ANTICIPA S A</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>1643132.54</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2268-87-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.608.700-2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>TBUSINESS SPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>77.009.886-6</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>63895.88</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>894244-5-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NTT DATA CHILE S.A</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>96.886.110-7</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>435941.1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2268-97-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.608.700-2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>83990.07000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>894244-4-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>1696277.88</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>812261-62-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>482098.69</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>730566-155-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61.980.240-3</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>77.754.348-2</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>55011.36</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>591-90-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>SONDA S A</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>83.628.100-4</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>913082.5600000001</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>591-86-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>1718926.68</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1607-76-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.509.000-k</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>BINARY BAG</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.848.560-7</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>752030.39</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>586-331-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>CLOUDHESIVE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>77.014.934-7</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>209143.07</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>591-293-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>73717.23</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>586-410-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>XMS Business Solutions S.A.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>16165.58</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2268-138-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>61.608.700-2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>CRUD SPA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>77.142.835-5</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>73043.13</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>761-270-CM26</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>60.515.000-4</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>76.011.651-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n">
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
         <v>128378.79</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>730566-175-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>61.980.240-3</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Fernando Marcelo</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>301925.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1749,7 +1749,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1810,7 +1814,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3847,7 +3855,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>586-370-CM25</t>
+          <t>586-402-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3887,12 +3895,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3902,13 +3910,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>151581.75</v>
+        <v>193181.61</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>586-402-CM25</t>
+          <t>586-370-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3948,12 +3956,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3963,7 +3971,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>193181.61</v>
+        <v>151581.75</v>
       </c>
     </row>
     <row r="57">
@@ -5111,7 +5119,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>812261-7571-CM25</t>
+          <t>812261-7572-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5159,20 +5167,24 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>291592.37</v>
+        <v>48887.01</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>812261-7571-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5220,14 +5232,18 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>48887.01</v>
+        <v>291592.37</v>
       </c>
     </row>
     <row r="77">
@@ -6472,7 +6488,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6883,7 +6903,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7009,7 +7029,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7110,6 +7130,258 @@
       </c>
       <c r="M106" s="2" t="n">
         <v>301925.55</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>586-452-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>USERCODE SPA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>77.347.464-8</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>64871.73</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2268-145-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>61.608.700-2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.802.163-5</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>15260.84</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>730566-262-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.980.240-3</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Fernando Marcelo</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>29710.85</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1216094-64-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>60.801.000-9</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>60966.87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
+++ b/docs/oc-top-organismos/desarrollo-y-mantencion-de-software-ti-e-iaas.xlsx
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
